--- a/results/tables/空间溢出权重矩阵.xlsx
+++ b/results/tables/空间溢出权重矩阵.xlsx
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1181262942836795</v>
+        <v>0.05796005292274831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2327621938856093</v>
+        <v>0.1431802960104945</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0852459688248117</v>
+        <v>0.03751731945104592</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1272562113185937</v>
+        <v>0.06400864774434425</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04539609371242138</v>
+        <v>0.01619414331916256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003883956890788862</v>
+        <v>0.0006105190238968334</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06110968150776714</v>
+        <v>0.02407021818801719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04927203281020227</v>
+        <v>0.01806344746641023</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0127011555795244</v>
+        <v>0.002963404807622489</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01142289099346694</v>
+        <v>0.03494073402815759</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06805634939194179</v>
+        <v>0.13324517362071</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03751731945104592</v>
+        <v>0.0852459688248117</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06805634939194179</v>
+        <v>0.13324517362071</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03567399334725239</v>
+        <v>0.0820849986238988</v>
       </c>
       <c r="H5" t="n">
-        <v>3.133109643125398e-05</v>
+        <v>0.0004187759137942209</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009489026566493544</v>
+        <v>0.005406500492658723</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002141255431924222</v>
+        <v>0.009954085305143469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02302358470854967</v>
+        <v>0.05910574656195623</v>
       </c>
     </row>
     <row r="6">
